--- a/CPDS-AD_dataset/scenario_records/FDI_attacks/local_model_consistent/test_data_LMC_4/data_three_phase_meter_3.xlsx
+++ b/CPDS-AD_dataset/scenario_records/FDI_attacks/local_model_consistent/test_data_LMC_4/data_three_phase_meter_3.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:02.245</t>
+          <t>2026/6/30 00:00:02.245</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -531,7 +531,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:06.932</t>
+          <t>2026/6/30 00:00:06.932</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -571,7 +571,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:11.582</t>
+          <t>2026/6/30 00:00:11.582</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:17.172</t>
+          <t>2026/6/30 00:00:17.172</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -651,7 +651,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:21.864</t>
+          <t>2026/6/30 00:00:21.864</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -691,7 +691,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:26.492</t>
+          <t>2026/6/30 00:00:26.492</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:31.189</t>
+          <t>2026/6/30 00:00:31.189</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -771,7 +771,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:36.146</t>
+          <t>2026/6/30 00:00:36.146</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:41.110</t>
+          <t>2026/6/30 00:00:41.110</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -851,7 +851,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:45.806</t>
+          <t>2026/6/30 00:00:45.806</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -891,7 +891,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:50.435</t>
+          <t>2026/6/30 00:00:50.435</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -931,7 +931,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026/6/29 23:00:56.350</t>
+          <t>2026/6/30 00:00:56.350</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:01.042</t>
+          <t>2026/6/30 00:01:01.042</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:05.693</t>
+          <t>2026/6/30 00:01:05.693</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:10.374</t>
+          <t>2026/6/30 00:01:10.374</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:15.628</t>
+          <t>2026/6/30 00:01:15.628</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:20.588</t>
+          <t>2026/6/30 00:01:20.588</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:25.249</t>
+          <t>2026/6/30 00:01:25.249</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:29.915</t>
+          <t>2026/6/30 00:01:29.915</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1251,7 +1251,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:34.894</t>
+          <t>2026/6/30 00:01:34.894</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:40.200</t>
+          <t>2026/6/30 00:01:40.200</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:44.833</t>
+          <t>2026/6/30 00:01:44.833</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:49.485</t>
+          <t>2026/6/30 00:01:49.485</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026/6/29 23:01:55.104</t>
+          <t>2026/6/30 00:01:55.104</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:00.062</t>
+          <t>2026/6/30 00:02:00.062</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:04.758</t>
+          <t>2026/6/30 00:02:04.758</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:09.404</t>
+          <t>2026/6/30 00:02:09.404</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:14.374</t>
+          <t>2026/6/30 00:02:14.374</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:19.681</t>
+          <t>2026/6/30 00:02:19.681</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:24.328</t>
+          <t>2026/6/30 00:02:24.328</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:28.983</t>
+          <t>2026/6/30 00:02:28.983</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:33.979</t>
+          <t>2026/6/30 00:02:33.979</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:39.257</t>
+          <t>2026/6/30 00:02:39.257</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:43.907</t>
+          <t>2026/6/30 00:02:43.907</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:48.579</t>
+          <t>2026/6/30 00:02:48.579</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:53.566</t>
+          <t>2026/6/30 00:02:53.566</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026/6/29 23:02:59.128</t>
+          <t>2026/6/30 00:02:59.128</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1971,7 +1971,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:03.834</t>
+          <t>2026/6/30 00:03:03.834</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:08.467</t>
+          <t>2026/6/30 00:03:08.467</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:13.454</t>
+          <t>2026/6/30 00:03:13.454</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:23.084</t>
+          <t>2026/6/30 00:03:23.084</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:27.729</t>
+          <t>2026/6/30 00:03:27.729</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:32.385</t>
+          <t>2026/6/30 00:03:32.385</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:38.014</t>
+          <t>2026/6/30 00:03:38.014</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:42.697</t>
+          <t>2026/6/30 00:03:42.697</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:47.319</t>
+          <t>2026/6/30 00:03:47.319</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:51.998</t>
+          <t>2026/6/30 00:03:51.998</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2371,7 +2371,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026/6/29 23:03:57.882</t>
+          <t>2026/6/30 00:03:57.882</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:02.581</t>
+          <t>2026/6/30 00:04:02.581</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:07.230</t>
+          <t>2026/6/30 00:04:07.230</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:11.873</t>
+          <t>2026/6/30 00:04:11.873</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -2531,7 +2531,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:16.560</t>
+          <t>2026/6/30 00:04:16.560</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:21.509</t>
+          <t>2026/6/30 00:04:21.509</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:26.185</t>
+          <t>2026/6/30 00:04:26.185</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:30.849</t>
+          <t>2026/6/30 00:04:30.849</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:36.126</t>
+          <t>2026/6/30 00:04:36.126</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:41.088</t>
+          <t>2026/6/30 00:04:41.088</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:45.749</t>
+          <t>2026/6/30 00:04:45.749</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:50.426</t>
+          <t>2026/6/30 00:04:50.426</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2026/6/29 23:04:56.350</t>
+          <t>2026/6/30 00:04:56.350</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:01.008</t>
+          <t>2026/6/30 00:05:01.008</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:06.265</t>
+          <t>2026/6/30 00:05:06.265</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:10.962</t>
+          <t>2026/6/30 00:05:10.962</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:16.264</t>
+          <t>2026/6/30 00:05:16.264</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:21.236</t>
+          <t>2026/6/30 00:05:21.236</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:25.855</t>
+          <t>2026/6/30 00:05:25.855</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:30.540</t>
+          <t>2026/6/30 00:05:30.540</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -3171,7 +3171,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:35.826</t>
+          <t>2026/6/30 00:05:35.826</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:40.778</t>
+          <t>2026/6/30 00:05:40.778</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:45.461</t>
+          <t>2026/6/30 00:05:45.461</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:50.131</t>
+          <t>2026/6/30 00:05:50.131</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2026/6/29 23:05:55.699</t>
+          <t>2026/6/30 00:05:55.699</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:00.680</t>
+          <t>2026/6/30 00:06:00.680</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:05.386</t>
+          <t>2026/6/30 00:06:05.386</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:10.015</t>
+          <t>2026/6/30 00:06:10.015</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:15.293</t>
+          <t>2026/6/30 00:06:15.293</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:20.288</t>
+          <t>2026/6/30 00:06:20.288</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -3571,7 +3571,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:24.942</t>
+          <t>2026/6/30 00:06:24.942</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:29.624</t>
+          <t>2026/6/30 00:06:29.624</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -3651,7 +3651,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:34.575</t>
+          <t>2026/6/30 00:06:34.575</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -3691,7 +3691,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:39.860</t>
+          <t>2026/6/30 00:06:39.860</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:44.507</t>
+          <t>2026/6/30 00:06:44.507</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:49.180</t>
+          <t>2026/6/30 00:06:49.180</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:54.459</t>
+          <t>2026/6/30 00:06:54.459</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2026/6/29 23:06:59.754</t>
+          <t>2026/6/30 00:06:59.754</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:04.737</t>
+          <t>2026/6/30 00:07:04.737</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:09.391</t>
+          <t>2026/6/30 00:07:09.391</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -3971,7 +3971,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:14.375</t>
+          <t>2026/6/30 00:07:14.375</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:19.653</t>
+          <t>2026/6/30 00:07:19.653</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:24.295</t>
+          <t>2026/6/30 00:07:24.295</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:28.964</t>
+          <t>2026/6/30 00:07:28.964</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:33.928</t>
+          <t>2026/6/30 00:07:33.928</t>
         </is>
       </c>
       <c r="C93" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:39.217</t>
+          <t>2026/6/30 00:07:39.217</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:43.901</t>
+          <t>2026/6/30 00:07:43.901</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:48.561</t>
+          <t>2026/6/30 00:07:48.561</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -4291,7 +4291,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2026/6/29 23:07:57.885</t>
+          <t>2026/6/30 00:07:57.885</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:02.518</t>
+          <t>2026/6/30 00:08:02.518</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:07.208</t>
+          <t>2026/6/30 00:08:07.208</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:11.862</t>
+          <t>2026/6/30 00:08:11.862</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:17.452</t>
+          <t>2026/6/30 00:08:17.452</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:22.124</t>
+          <t>2026/6/30 00:08:22.124</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:26.769</t>
+          <t>2026/6/30 00:08:26.769</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -4571,7 +4571,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:31.440</t>
+          <t>2026/6/30 00:08:31.440</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -4611,7 +4611,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:36.747</t>
+          <t>2026/6/30 00:08:36.747</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:41.734</t>
+          <t>2026/6/30 00:08:41.734</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:46.380</t>
+          <t>2026/6/30 00:08:46.380</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:51.072</t>
+          <t>2026/6/30 00:08:51.072</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2026/6/29 23:08:56.947</t>
+          <t>2026/6/30 00:08:56.947</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:01.616</t>
+          <t>2026/6/30 00:09:01.616</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:06.275</t>
+          <t>2026/6/30 00:09:06.275</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -4891,7 +4891,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:10.970</t>
+          <t>2026/6/30 00:09:10.970</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:16.257</t>
+          <t>2026/6/30 00:09:16.257</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:21.218</t>
+          <t>2026/6/30 00:09:21.218</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:25.881</t>
+          <t>2026/6/30 00:09:25.881</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:30.534</t>
+          <t>2026/6/30 00:09:30.534</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:35.793</t>
+          <t>2026/6/30 00:09:35.793</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:40.793</t>
+          <t>2026/6/30 00:09:40.793</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -5171,7 +5171,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:45.431</t>
+          <t>2026/6/30 00:09:45.431</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:50.122</t>
+          <t>2026/6/30 00:09:50.122</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -5251,7 +5251,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026/6/29 23:09:55.697</t>
+          <t>2026/6/30 00:09:55.697</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:00.670</t>
+          <t>2026/6/30 00:10:00.670</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:05.349</t>
+          <t>2026/6/30 00:10:05.349</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:09.990</t>
+          <t>2026/6/30 00:10:09.990</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:15.262</t>
+          <t>2026/6/30 00:10:15.262</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -5451,7 +5451,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:20.271</t>
+          <t>2026/6/30 00:10:20.271</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:24.906</t>
+          <t>2026/6/30 00:10:24.906</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:29.595</t>
+          <t>2026/6/30 00:10:29.595</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:34.578</t>
+          <t>2026/6/30 00:10:34.578</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:39.862</t>
+          <t>2026/6/30 00:10:39.862</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -5651,7 +5651,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:44.491</t>
+          <t>2026/6/30 00:10:44.491</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:49.176</t>
+          <t>2026/6/30 00:10:49.176</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:54.453</t>
+          <t>2026/6/30 00:10:54.453</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2026/6/29 23:10:59.738</t>
+          <t>2026/6/30 00:10:59.738</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:04.401</t>
+          <t>2026/6/30 00:11:04.401</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:09.044</t>
+          <t>2026/6/30 00:11:09.044</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:14.033</t>
+          <t>2026/6/30 00:11:14.033</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:19.355</t>
+          <t>2026/6/30 00:11:19.355</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -5971,7 +5971,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:24.005</t>
+          <t>2026/6/30 00:11:24.005</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:28.646</t>
+          <t>2026/6/30 00:11:28.646</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:33.613</t>
+          <t>2026/6/30 00:11:33.613</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -6091,7 +6091,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:42.968</t>
+          <t>2026/6/30 00:11:42.968</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:47.588</t>
+          <t>2026/6/30 00:11:47.588</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:52.299</t>
+          <t>2026/6/30 00:11:52.299</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2026/6/29 23:11:58.176</t>
+          <t>2026/6/30 00:11:58.176</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -6251,7 +6251,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:02.846</t>
+          <t>2026/6/30 00:12:02.846</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:07.509</t>
+          <t>2026/6/30 00:12:07.509</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:12.184</t>
+          <t>2026/6/30 00:12:12.184</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:17.748</t>
+          <t>2026/6/30 00:12:17.748</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -6411,7 +6411,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:22.448</t>
+          <t>2026/6/30 00:12:22.448</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -6451,7 +6451,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:27.082</t>
+          <t>2026/6/30 00:12:27.082</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:31.755</t>
+          <t>2026/6/30 00:12:31.755</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:37.034</t>
+          <t>2026/6/30 00:12:37.034</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -6571,7 +6571,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:41.728</t>
+          <t>2026/6/30 00:12:41.728</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:46.387</t>
+          <t>2026/6/30 00:12:46.387</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:51.016</t>
+          <t>2026/6/30 00:12:51.016</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>2026/6/29 23:12:56.945</t>
+          <t>2026/6/30 00:12:56.945</t>
         </is>
       </c>
       <c r="C157" t="n">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:01.631</t>
+          <t>2026/6/30 00:13:01.631</t>
         </is>
       </c>
       <c r="C158" t="n">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:06.295</t>
+          <t>2026/6/30 00:13:06.295</t>
         </is>
       </c>
       <c r="C159" t="n">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:10.898</t>
+          <t>2026/6/30 00:13:10.898</t>
         </is>
       </c>
       <c r="C160" t="n">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:16.221</t>
+          <t>2026/6/30 00:13:16.221</t>
         </is>
       </c>
       <c r="C161" t="n">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:21.192</t>
+          <t>2026/6/30 00:13:21.192</t>
         </is>
       </c>
       <c r="C162" t="n">
@@ -6931,7 +6931,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:25.816</t>
+          <t>2026/6/30 00:13:25.816</t>
         </is>
       </c>
       <c r="C163" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:30.536</t>
+          <t>2026/6/30 00:13:30.536</t>
         </is>
       </c>
       <c r="C164" t="n">
@@ -7011,7 +7011,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:35.784</t>
+          <t>2026/6/30 00:13:35.784</t>
         </is>
       </c>
       <c r="C165" t="n">
@@ -7051,7 +7051,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:40.766</t>
+          <t>2026/6/30 00:13:40.766</t>
         </is>
       </c>
       <c r="C166" t="n">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:45.455</t>
+          <t>2026/6/30 00:13:45.455</t>
         </is>
       </c>
       <c r="C167" t="n">
@@ -7131,7 +7131,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:50.106</t>
+          <t>2026/6/30 00:13:50.106</t>
         </is>
       </c>
       <c r="C168" t="n">
@@ -7171,7 +7171,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>2026/6/29 23:13:55.694</t>
+          <t>2026/6/30 00:13:55.694</t>
         </is>
       </c>
       <c r="C169" t="n">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:00.664</t>
+          <t>2026/6/30 00:14:00.664</t>
         </is>
       </c>
       <c r="C170" t="n">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:05.343</t>
+          <t>2026/6/30 00:14:05.343</t>
         </is>
       </c>
       <c r="C171" t="n">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:09.989</t>
+          <t>2026/6/30 00:14:09.989</t>
         </is>
       </c>
       <c r="C172" t="n">
@@ -7331,7 +7331,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:15.270</t>
+          <t>2026/6/30 00:14:15.270</t>
         </is>
       </c>
       <c r="C173" t="n">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:20.230</t>
+          <t>2026/6/30 00:14:20.230</t>
         </is>
       </c>
       <c r="C174" t="n">
@@ -7411,7 +7411,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:24.896</t>
+          <t>2026/6/30 00:14:24.896</t>
         </is>
       </c>
       <c r="C175" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:29.558</t>
+          <t>2026/6/30 00:14:29.558</t>
         </is>
       </c>
       <c r="C176" t="n">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:34.540</t>
+          <t>2026/6/30 00:14:34.540</t>
         </is>
       </c>
       <c r="C177" t="n">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:39.815</t>
+          <t>2026/6/30 00:14:39.815</t>
         </is>
       </c>
       <c r="C178" t="n">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:44.521</t>
+          <t>2026/6/30 00:14:44.521</t>
         </is>
       </c>
       <c r="C179" t="n">
@@ -7611,7 +7611,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:49.187</t>
+          <t>2026/6/30 00:14:49.187</t>
         </is>
       </c>
       <c r="C180" t="n">
@@ -7651,7 +7651,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:54.417</t>
+          <t>2026/6/30 00:14:54.417</t>
         </is>
       </c>
       <c r="C181" t="n">
@@ -7691,7 +7691,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>2026/6/29 23:14:59.728</t>
+          <t>2026/6/30 00:14:59.728</t>
         </is>
       </c>
       <c r="C182" t="n">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:04.379</t>
+          <t>2026/6/30 00:15:04.379</t>
         </is>
       </c>
       <c r="C183" t="n">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:09.035</t>
+          <t>2026/6/30 00:15:09.035</t>
         </is>
       </c>
       <c r="C184" t="n">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:14.039</t>
+          <t>2026/6/30 00:15:14.039</t>
         </is>
       </c>
       <c r="C185" t="n">
@@ -7851,7 +7851,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:19.023</t>
+          <t>2026/6/30 00:15:19.023</t>
         </is>
       </c>
       <c r="C186" t="n">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:23.676</t>
+          <t>2026/6/30 00:15:23.676</t>
         </is>
       </c>
       <c r="C187" t="n">
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:32.998</t>
+          <t>2026/6/30 00:15:32.998</t>
         </is>
       </c>
       <c r="C188" t="n">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:38.571</t>
+          <t>2026/6/30 00:15:38.571</t>
         </is>
       </c>
       <c r="C189" t="n">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:43.255</t>
+          <t>2026/6/30 00:15:43.255</t>
         </is>
       </c>
       <c r="C190" t="n">
@@ -8051,7 +8051,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:47.898</t>
+          <t>2026/6/30 00:15:47.898</t>
         </is>
       </c>
       <c r="C191" t="n">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:52.553</t>
+          <t>2026/6/30 00:15:52.553</t>
         </is>
       </c>
       <c r="C192" t="n">
@@ -8131,7 +8131,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>2026/6/29 23:15:58.499</t>
+          <t>2026/6/30 00:15:58.499</t>
         </is>
       </c>
       <c r="C193" t="n">
@@ -8171,7 +8171,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:03.164</t>
+          <t>2026/6/30 00:16:03.164</t>
         </is>
       </c>
       <c r="C194" t="n">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:07.812</t>
+          <t>2026/6/30 00:16:07.812</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -8251,7 +8251,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:12.451</t>
+          <t>2026/6/30 00:16:12.451</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -8291,7 +8291,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:17.453</t>
+          <t>2026/6/30 00:16:17.453</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:22.097</t>
+          <t>2026/6/30 00:16:22.097</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -8371,7 +8371,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:26.747</t>
+          <t>2026/6/30 00:16:26.747</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:31.415</t>
+          <t>2026/6/30 00:16:31.415</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -8451,7 +8451,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:36.706</t>
+          <t>2026/6/30 00:16:36.706</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:41.702</t>
+          <t>2026/6/30 00:16:41.702</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:46.362</t>
+          <t>2026/6/30 00:16:46.362</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -8571,7 +8571,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:51.000</t>
+          <t>2026/6/30 00:16:51.000</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>2026/6/29 23:16:56.908</t>
+          <t>2026/6/30 00:16:56.908</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:01.591</t>
+          <t>2026/6/30 00:17:01.591</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:06.224</t>
+          <t>2026/6/30 00:17:06.224</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:10.886</t>
+          <t>2026/6/30 00:17:10.886</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:16.183</t>
+          <t>2026/6/30 00:17:16.183</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:21.162</t>
+          <t>2026/6/30 00:17:21.162</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -8851,7 +8851,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:25.820</t>
+          <t>2026/6/30 00:17:25.820</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -8891,7 +8891,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:30.494</t>
+          <t>2026/6/30 00:17:30.494</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -8931,7 +8931,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:35.792</t>
+          <t>2026/6/30 00:17:35.792</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:40.758</t>
+          <t>2026/6/30 00:17:40.758</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:45.416</t>
+          <t>2026/6/30 00:17:45.416</t>
         </is>
       </c>
       <c r="C215" t="n">
@@ -9051,7 +9051,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:50.058</t>
+          <t>2026/6/30 00:17:50.058</t>
         </is>
       </c>
       <c r="C216" t="n">
@@ -9091,7 +9091,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>2026/6/29 23:17:55.685</t>
+          <t>2026/6/30 00:17:55.685</t>
         </is>
       </c>
       <c r="C217" t="n">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:00.630</t>
+          <t>2026/6/30 00:18:00.630</t>
         </is>
       </c>
       <c r="C218" t="n">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:05.337</t>
+          <t>2026/6/30 00:18:05.337</t>
         </is>
       </c>
       <c r="C219" t="n">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:09.984</t>
+          <t>2026/6/30 00:18:09.984</t>
         </is>
       </c>
       <c r="C220" t="n">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:14.916</t>
+          <t>2026/6/30 00:18:14.916</t>
         </is>
       </c>
       <c r="C221" t="n">
@@ -9291,7 +9291,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:20.248</t>
+          <t>2026/6/30 00:18:20.248</t>
         </is>
       </c>
       <c r="C222" t="n">
@@ -9331,7 +9331,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:24.891</t>
+          <t>2026/6/30 00:18:24.891</t>
         </is>
       </c>
       <c r="C223" t="n">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:29.527</t>
+          <t>2026/6/30 00:18:29.527</t>
         </is>
       </c>
       <c r="C224" t="n">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:34.509</t>
+          <t>2026/6/30 00:18:34.509</t>
         </is>
       </c>
       <c r="C225" t="n">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:39.789</t>
+          <t>2026/6/30 00:18:39.789</t>
         </is>
       </c>
       <c r="C226" t="n">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:44.462</t>
+          <t>2026/6/30 00:18:44.462</t>
         </is>
       </c>
       <c r="C227" t="n">
@@ -9531,7 +9531,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:49.130</t>
+          <t>2026/6/30 00:18:49.130</t>
         </is>
       </c>
       <c r="C228" t="n">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:54.418</t>
+          <t>2026/6/30 00:18:54.418</t>
         </is>
       </c>
       <c r="C229" t="n">
@@ -9611,7 +9611,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>2026/6/29 23:18:59.707</t>
+          <t>2026/6/30 00:18:59.707</t>
         </is>
       </c>
       <c r="C230" t="n">
@@ -9651,7 +9651,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:04.340</t>
+          <t>2026/6/30 00:19:04.340</t>
         </is>
       </c>
       <c r="C231" t="n">
@@ -9691,7 +9691,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:09.044</t>
+          <t>2026/6/30 00:19:09.044</t>
         </is>
       </c>
       <c r="C232" t="n">
@@ -9731,7 +9731,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:13.988</t>
+          <t>2026/6/30 00:19:13.988</t>
         </is>
       </c>
       <c r="C233" t="n">
@@ -9771,7 +9771,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:19.276</t>
+          <t>2026/6/30 00:19:19.276</t>
         </is>
       </c>
       <c r="C234" t="n">
@@ -9811,7 +9811,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:23.921</t>
+          <t>2026/6/30 00:19:23.921</t>
         </is>
       </c>
       <c r="C235" t="n">
@@ -9851,7 +9851,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:28.592</t>
+          <t>2026/6/30 00:19:28.592</t>
         </is>
       </c>
       <c r="C236" t="n">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:33.575</t>
+          <t>2026/6/30 00:19:33.575</t>
         </is>
       </c>
       <c r="C237" t="n">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:38.842</t>
+          <t>2026/6/30 00:19:38.842</t>
         </is>
       </c>
       <c r="C238" t="n">
@@ -9971,7 +9971,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:48.214</t>
+          <t>2026/6/30 00:19:48.214</t>
         </is>
       </c>
       <c r="C239" t="n">
@@ -10011,7 +10011,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:52.853</t>
+          <t>2026/6/30 00:19:52.853</t>
         </is>
       </c>
       <c r="C240" t="n">
@@ -10051,7 +10051,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>2026/6/29 23:19:57.827</t>
+          <t>2026/6/30 00:19:57.827</t>
         </is>
       </c>
       <c r="C241" t="n">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:02.807</t>
+          <t>2026/6/30 00:20:02.807</t>
         </is>
       </c>
       <c r="C242" t="n">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:07.498</t>
+          <t>2026/6/30 00:20:07.498</t>
         </is>
       </c>
       <c r="C243" t="n">
@@ -10171,7 +10171,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:12.152</t>
+          <t>2026/6/30 00:20:12.152</t>
         </is>
       </c>
       <c r="C244" t="n">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:17.718</t>
+          <t>2026/6/30 00:20:17.718</t>
         </is>
       </c>
       <c r="C245" t="n">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:22.411</t>
+          <t>2026/6/30 00:20:22.411</t>
         </is>
       </c>
       <c r="C246" t="n">
@@ -10291,7 +10291,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:27.037</t>
+          <t>2026/6/30 00:20:27.037</t>
         </is>
       </c>
       <c r="C247" t="n">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:31.715</t>
+          <t>2026/6/30 00:20:31.715</t>
         </is>
       </c>
       <c r="C248" t="n">
@@ -10371,7 +10371,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:36.998</t>
+          <t>2026/6/30 00:20:36.998</t>
         </is>
       </c>
       <c r="C249" t="n">
@@ -10411,7 +10411,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:41.993</t>
+          <t>2026/6/30 00:20:41.993</t>
         </is>
       </c>
       <c r="C250" t="n">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:46.664</t>
+          <t>2026/6/30 00:20:46.664</t>
         </is>
       </c>
       <c r="C251" t="n">
@@ -10491,7 +10491,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:51.278</t>
+          <t>2026/6/30 00:20:51.278</t>
         </is>
       </c>
       <c r="C252" t="n">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>2026/6/29 23:20:56.878</t>
+          <t>2026/6/30 00:20:56.878</t>
         </is>
       </c>
       <c r="C253" t="n">
@@ -10571,7 +10571,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:01.548</t>
+          <t>2026/6/30 00:21:01.548</t>
         </is>
       </c>
       <c r="C254" t="n">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:06.249</t>
+          <t>2026/6/30 00:21:06.249</t>
         </is>
       </c>
       <c r="C255" t="n">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:10.896</t>
+          <t>2026/6/30 00:21:10.896</t>
         </is>
       </c>
       <c r="C256" t="n">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:16.177</t>
+          <t>2026/6/30 00:21:16.177</t>
         </is>
       </c>
       <c r="C257" t="n">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:21.130</t>
+          <t>2026/6/30 00:21:21.130</t>
         </is>
       </c>
       <c r="C258" t="n">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:25.812</t>
+          <t>2026/6/30 00:21:25.812</t>
         </is>
       </c>
       <c r="C259" t="n">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:30.478</t>
+          <t>2026/6/30 00:21:30.478</t>
         </is>
       </c>
       <c r="C260" t="n">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:35.769</t>
+          <t>2026/6/30 00:21:35.769</t>
         </is>
       </c>
       <c r="C261" t="n">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:40.739</t>
+          <t>2026/6/30 00:21:40.739</t>
         </is>
       </c>
       <c r="C262" t="n">
@@ -10931,7 +10931,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:45.400</t>
+          <t>2026/6/30 00:21:45.400</t>
         </is>
       </c>
       <c r="C263" t="n">
@@ -10971,7 +10971,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:50.027</t>
+          <t>2026/6/30 00:21:50.027</t>
         </is>
       </c>
       <c r="C264" t="n">
@@ -11011,7 +11011,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>2026/6/29 23:21:55.658</t>
+          <t>2026/6/30 00:21:55.658</t>
         </is>
       </c>
       <c r="C265" t="n">
@@ -11051,7 +11051,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:00.615</t>
+          <t>2026/6/30 00:22:00.615</t>
         </is>
       </c>
       <c r="C266" t="n">
@@ -11091,7 +11091,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:05.287</t>
+          <t>2026/6/30 00:22:05.287</t>
         </is>
       </c>
       <c r="C267" t="n">
@@ -11131,7 +11131,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:09.941</t>
+          <t>2026/6/30 00:22:09.941</t>
         </is>
       </c>
       <c r="C268" t="n">
@@ -11171,7 +11171,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:14.893</t>
+          <t>2026/6/30 00:22:14.893</t>
         </is>
       </c>
       <c r="C269" t="n">
@@ -11211,7 +11211,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:20.216</t>
+          <t>2026/6/30 00:22:20.216</t>
         </is>
       </c>
       <c r="C270" t="n">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:24.885</t>
+          <t>2026/6/30 00:22:24.885</t>
         </is>
       </c>
       <c r="C271" t="n">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:29.538</t>
+          <t>2026/6/30 00:22:29.538</t>
         </is>
       </c>
       <c r="C272" t="n">
@@ -11331,7 +11331,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:34.500</t>
+          <t>2026/6/30 00:22:34.500</t>
         </is>
       </c>
       <c r="C273" t="n">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:39.809</t>
+          <t>2026/6/30 00:22:39.809</t>
         </is>
       </c>
       <c r="C274" t="n">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:44.480</t>
+          <t>2026/6/30 00:22:44.480</t>
         </is>
       </c>
       <c r="C275" t="n">
@@ -11451,7 +11451,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:49.143</t>
+          <t>2026/6/30 00:22:49.143</t>
         </is>
       </c>
       <c r="C276" t="n">
@@ -11491,7 +11491,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:54.417</t>
+          <t>2026/6/30 00:22:54.417</t>
         </is>
       </c>
       <c r="C277" t="n">
@@ -11531,7 +11531,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>2026/6/29 23:22:59.694</t>
+          <t>2026/6/30 00:22:59.694</t>
         </is>
       </c>
       <c r="C278" t="n">
@@ -11571,7 +11571,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:04.345</t>
+          <t>2026/6/30 00:23:04.345</t>
         </is>
       </c>
       <c r="C279" t="n">
@@ -11611,7 +11611,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:09.017</t>
+          <t>2026/6/30 00:23:09.017</t>
         </is>
       </c>
       <c r="C280" t="n">
@@ -11651,7 +11651,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:13.985</t>
+          <t>2026/6/30 00:23:13.985</t>
         </is>
       </c>
       <c r="C281" t="n">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:19.285</t>
+          <t>2026/6/30 00:23:19.285</t>
         </is>
       </c>
       <c r="C282" t="n">
@@ -11731,7 +11731,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:23.957</t>
+          <t>2026/6/30 00:23:23.957</t>
         </is>
       </c>
       <c r="C283" t="n">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:28.587</t>
+          <t>2026/6/30 00:23:28.587</t>
         </is>
       </c>
       <c r="C284" t="n">
@@ -11811,7 +11811,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:33.606</t>
+          <t>2026/6/30 00:23:33.606</t>
         </is>
       </c>
       <c r="C285" t="n">
@@ -11851,7 +11851,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:38.569</t>
+          <t>2026/6/30 00:23:38.569</t>
         </is>
       </c>
       <c r="C286" t="n">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:48.201</t>
+          <t>2026/6/30 00:23:48.201</t>
         </is>
       </c>
       <c r="C287" t="n">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:53.156</t>
+          <t>2026/6/30 00:23:53.156</t>
         </is>
       </c>
       <c r="C288" t="n">
@@ -11971,7 +11971,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:58.736</t>
+          <t>2026/6/30 00:23:58.736</t>
         </is>
       </c>
       <c r="C289" t="n">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>2026/6/29 23:23:58.736</t>
+          <t>2026/6/30 00:23:58.736</t>
         </is>
       </c>
       <c r="C290" t="n">
@@ -12051,7 +12051,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:08.118</t>
+          <t>2026/6/30 00:24:08.118</t>
         </is>
       </c>
       <c r="C291" t="n">
@@ -12091,7 +12091,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:12.728</t>
+          <t>2026/6/30 00:24:12.728</t>
         </is>
       </c>
       <c r="C292" t="n">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:18.320</t>
+          <t>2026/6/30 00:24:18.320</t>
         </is>
       </c>
       <c r="C293" t="n">
@@ -12171,7 +12171,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:23.005</t>
+          <t>2026/6/30 00:24:23.005</t>
         </is>
       </c>
       <c r="C294" t="n">
@@ -12211,7 +12211,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:27.687</t>
+          <t>2026/6/30 00:24:27.687</t>
         </is>
       </c>
       <c r="C295" t="n">
@@ -12251,7 +12251,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:32.314</t>
+          <t>2026/6/30 00:24:32.314</t>
         </is>
       </c>
       <c r="C296" t="n">
@@ -12291,7 +12291,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:37.327</t>
+          <t>2026/6/30 00:24:37.327</t>
         </is>
       </c>
       <c r="C297" t="n">
@@ -12331,7 +12331,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:41.968</t>
+          <t>2026/6/30 00:24:41.968</t>
         </is>
       </c>
       <c r="C298" t="n">
@@ -12371,7 +12371,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:46.655</t>
+          <t>2026/6/30 00:24:46.655</t>
         </is>
       </c>
       <c r="C299" t="n">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:51.294</t>
+          <t>2026/6/30 00:24:51.294</t>
         </is>
       </c>
       <c r="C300" t="n">
@@ -12451,7 +12451,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>2026/6/29 23:24:57.201</t>
+          <t>2026/6/30 00:24:57.201</t>
         </is>
       </c>
       <c r="C301" t="n">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:01.852</t>
+          <t>2026/6/30 00:25:01.852</t>
         </is>
       </c>
       <c r="C302" t="n">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:06.538</t>
+          <t>2026/6/30 00:25:06.538</t>
         </is>
       </c>
       <c r="C303" t="n">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:11.221</t>
+          <t>2026/6/30 00:25:11.221</t>
         </is>
       </c>
       <c r="C304" t="n">
@@ -12611,7 +12611,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:16.471</t>
+          <t>2026/6/30 00:25:16.471</t>
         </is>
       </c>
       <c r="C305" t="n">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:21.448</t>
+          <t>2026/6/30 00:25:21.448</t>
         </is>
       </c>
       <c r="C306" t="n">
@@ -12691,7 +12691,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:26.111</t>
+          <t>2026/6/30 00:25:26.111</t>
         </is>
       </c>
       <c r="C307" t="n">
@@ -12731,7 +12731,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:30.770</t>
+          <t>2026/6/30 00:25:30.770</t>
         </is>
       </c>
       <c r="C308" t="n">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:36.040</t>
+          <t>2026/6/30 00:25:36.040</t>
         </is>
       </c>
       <c r="C309" t="n">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:41.073</t>
+          <t>2026/6/30 00:25:41.073</t>
         </is>
       </c>
       <c r="C310" t="n">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:45.702</t>
+          <t>2026/6/30 00:25:45.702</t>
         </is>
       </c>
       <c r="C311" t="n">
@@ -12891,7 +12891,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:50.369</t>
+          <t>2026/6/30 00:25:50.369</t>
         </is>
       </c>
       <c r="C312" t="n">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>2026/6/29 23:25:56.242</t>
+          <t>2026/6/30 00:25:56.242</t>
         </is>
       </c>
       <c r="C313" t="n">
@@ -12971,7 +12971,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:00.939</t>
+          <t>2026/6/30 00:26:00.939</t>
         </is>
       </c>
       <c r="C314" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:05.625</t>
+          <t>2026/6/30 00:26:05.625</t>
         </is>
       </c>
       <c r="C315" t="n">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:10.235</t>
+          <t>2026/6/30 00:26:10.235</t>
         </is>
       </c>
       <c r="C316" t="n">
@@ -13091,7 +13091,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:15.531</t>
+          <t>2026/6/30 00:26:15.531</t>
         </is>
       </c>
       <c r="C317" t="n">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:20.531</t>
+          <t>2026/6/30 00:26:20.531</t>
         </is>
       </c>
       <c r="C318" t="n">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:25.177</t>
+          <t>2026/6/30 00:26:25.177</t>
         </is>
       </c>
       <c r="C319" t="n">
@@ -13211,7 +13211,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:29.812</t>
+          <t>2026/6/30 00:26:29.812</t>
         </is>
       </c>
       <c r="C320" t="n">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:35.133</t>
+          <t>2026/6/30 00:26:35.133</t>
         </is>
       </c>
       <c r="C321" t="n">
@@ -13291,7 +13291,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:40.102</t>
+          <t>2026/6/30 00:26:40.102</t>
         </is>
       </c>
       <c r="C322" t="n">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:44.765</t>
+          <t>2026/6/30 00:26:44.765</t>
         </is>
       </c>
       <c r="C323" t="n">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:49.423</t>
+          <t>2026/6/30 00:26:49.423</t>
         </is>
       </c>
       <c r="C324" t="n">
@@ -13411,7 +13411,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>2026/6/29 23:26:54.737</t>
+          <t>2026/6/30 00:26:54.737</t>
         </is>
       </c>
       <c r="C325" t="n">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:00.029</t>
+          <t>2026/6/30 00:27:00.029</t>
         </is>
       </c>
       <c r="C326" t="n">
@@ -13491,7 +13491,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:04.672</t>
+          <t>2026/6/30 00:27:04.672</t>
         </is>
       </c>
       <c r="C327" t="n">
@@ -13531,7 +13531,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:09.289</t>
+          <t>2026/6/30 00:27:09.289</t>
         </is>
       </c>
       <c r="C328" t="n">
@@ -13571,7 +13571,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:14.328</t>
+          <t>2026/6/30 00:27:14.328</t>
         </is>
       </c>
       <c r="C329" t="n">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:19.610</t>
+          <t>2026/6/30 00:27:19.610</t>
         </is>
       </c>
       <c r="C330" t="n">
@@ -13651,7 +13651,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:24.564</t>
+          <t>2026/6/30 00:27:24.564</t>
         </is>
       </c>
       <c r="C331" t="n">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:29.212</t>
+          <t>2026/6/30 00:27:29.212</t>
         </is>
       </c>
       <c r="C332" t="n">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:34.200</t>
+          <t>2026/6/30 00:27:34.200</t>
         </is>
       </c>
       <c r="C333" t="n">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:39.502</t>
+          <t>2026/6/30 00:27:39.502</t>
         </is>
       </c>
       <c r="C334" t="n">
@@ -13811,7 +13811,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:44.123</t>
+          <t>2026/6/30 00:27:44.123</t>
         </is>
       </c>
       <c r="C335" t="n">
@@ -13851,7 +13851,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:48.784</t>
+          <t>2026/6/30 00:27:48.784</t>
         </is>
       </c>
       <c r="C336" t="n">
@@ -13891,7 +13891,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:54.099</t>
+          <t>2026/6/30 00:27:54.099</t>
         </is>
       </c>
       <c r="C337" t="n">
@@ -13931,7 +13931,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>2026/6/29 23:27:59.369</t>
+          <t>2026/6/30 00:27:59.369</t>
         </is>
       </c>
       <c r="C338" t="n">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:04.029</t>
+          <t>2026/6/30 00:28:04.029</t>
         </is>
       </c>
       <c r="C339" t="n">
@@ -14011,7 +14011,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:08.702</t>
+          <t>2026/6/30 00:28:08.702</t>
         </is>
       </c>
       <c r="C340" t="n">
@@ -14051,7 +14051,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:18.020</t>
+          <t>2026/6/30 00:28:18.020</t>
         </is>
       </c>
       <c r="C341" t="n">
@@ -14091,7 +14091,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:22.667</t>
+          <t>2026/6/30 00:28:22.667</t>
         </is>
       </c>
       <c r="C342" t="n">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:27.335</t>
+          <t>2026/6/30 00:28:27.335</t>
         </is>
       </c>
       <c r="C343" t="n">
@@ -14171,7 +14171,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:31.993</t>
+          <t>2026/6/30 00:28:31.993</t>
         </is>
       </c>
       <c r="C344" t="n">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:37.614</t>
+          <t>2026/6/30 00:28:37.614</t>
         </is>
       </c>
       <c r="C345" t="n">
@@ -14251,7 +14251,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:42.266</t>
+          <t>2026/6/30 00:28:42.266</t>
         </is>
       </c>
       <c r="C346" t="n">
@@ -14291,7 +14291,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:46.928</t>
+          <t>2026/6/30 00:28:46.928</t>
         </is>
       </c>
       <c r="C347" t="n">
@@ -14331,7 +14331,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:51.618</t>
+          <t>2026/6/30 00:28:51.618</t>
         </is>
       </c>
       <c r="C348" t="n">
@@ -14371,7 +14371,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>2026/6/29 23:28:57.529</t>
+          <t>2026/6/30 00:28:57.529</t>
         </is>
       </c>
       <c r="C349" t="n">
@@ -14411,7 +14411,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:02.175</t>
+          <t>2026/6/30 00:29:02.175</t>
         </is>
       </c>
       <c r="C350" t="n">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:06.806</t>
+          <t>2026/6/30 00:29:06.806</t>
         </is>
       </c>
       <c r="C351" t="n">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:11.498</t>
+          <t>2026/6/30 00:29:11.498</t>
         </is>
       </c>
       <c r="C352" t="n">
@@ -14531,7 +14531,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:16.757</t>
+          <t>2026/6/30 00:29:16.757</t>
         </is>
       </c>
       <c r="C353" t="n">
@@ -14571,7 +14571,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:21.762</t>
+          <t>2026/6/30 00:29:21.762</t>
         </is>
       </c>
       <c r="C354" t="n">
@@ -14611,7 +14611,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:26.405</t>
+          <t>2026/6/30 00:29:26.405</t>
         </is>
       </c>
       <c r="C355" t="n">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:31.068</t>
+          <t>2026/6/30 00:29:31.068</t>
         </is>
       </c>
       <c r="C356" t="n">
@@ -14691,7 +14691,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:36.339</t>
+          <t>2026/6/30 00:29:36.339</t>
         </is>
       </c>
       <c r="C357" t="n">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:41.328</t>
+          <t>2026/6/30 00:29:41.328</t>
         </is>
       </c>
       <c r="C358" t="n">
@@ -14771,7 +14771,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:45.992</t>
+          <t>2026/6/30 00:29:45.992</t>
         </is>
       </c>
       <c r="C359" t="n">
@@ -14811,7 +14811,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:50.672</t>
+          <t>2026/6/30 00:29:50.672</t>
         </is>
       </c>
       <c r="C360" t="n">
@@ -14851,7 +14851,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>2026/6/29 23:29:56.575</t>
+          <t>2026/6/30 00:29:56.575</t>
         </is>
       </c>
       <c r="C361" t="n">
@@ -14891,7 +14891,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:01.238</t>
+          <t>2026/6/30 00:30:01.238</t>
         </is>
       </c>
       <c r="C362" t="n">
@@ -14931,7 +14931,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:05.891</t>
+          <t>2026/6/30 00:30:05.891</t>
         </is>
       </c>
       <c r="C363" t="n">
@@ -14971,7 +14971,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:10.528</t>
+          <t>2026/6/30 00:30:10.528</t>
         </is>
       </c>
       <c r="C364" t="n">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:15.836</t>
+          <t>2026/6/30 00:30:15.836</t>
         </is>
       </c>
       <c r="C365" t="n">
@@ -15051,7 +15051,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:20.788</t>
+          <t>2026/6/30 00:30:20.788</t>
         </is>
       </c>
       <c r="C366" t="n">
@@ -15091,7 +15091,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:25.487</t>
+          <t>2026/6/30 00:30:25.487</t>
         </is>
       </c>
       <c r="C367" t="n">
@@ -15131,7 +15131,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:30.109</t>
+          <t>2026/6/30 00:30:30.109</t>
         </is>
       </c>
       <c r="C368" t="n">
@@ -15171,7 +15171,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:35.422</t>
+          <t>2026/6/30 00:30:35.422</t>
         </is>
       </c>
       <c r="C369" t="n">
@@ -15211,7 +15211,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:40.373</t>
+          <t>2026/6/30 00:30:40.373</t>
         </is>
       </c>
       <c r="C370" t="n">
@@ -15251,7 +15251,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:45.027</t>
+          <t>2026/6/30 00:30:45.027</t>
         </is>
       </c>
       <c r="C371" t="n">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:49.707</t>
+          <t>2026/6/30 00:30:49.707</t>
         </is>
       </c>
       <c r="C372" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>2026/6/29 23:30:55.304</t>
+          <t>2026/6/30 00:30:55.304</t>
         </is>
       </c>
       <c r="C373" t="n">
@@ -15371,7 +15371,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:00.284</t>
+          <t>2026/6/30 00:31:00.284</t>
         </is>
       </c>
       <c r="C374" t="n">
@@ -15411,7 +15411,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:04.945</t>
+          <t>2026/6/30 00:31:04.945</t>
         </is>
       </c>
       <c r="C375" t="n">
@@ -15451,7 +15451,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:09.589</t>
+          <t>2026/6/30 00:31:09.589</t>
         </is>
       </c>
       <c r="C376" t="n">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:14.599</t>
+          <t>2026/6/30 00:31:14.599</t>
         </is>
       </c>
       <c r="C377" t="n">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:19.854</t>
+          <t>2026/6/30 00:31:19.854</t>
         </is>
       </c>
       <c r="C378" t="n">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:24.541</t>
+          <t>2026/6/30 00:31:24.541</t>
         </is>
       </c>
       <c r="C379" t="n">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:29.191</t>
+          <t>2026/6/30 00:31:29.191</t>
         </is>
       </c>
       <c r="C380" t="n">
@@ -15651,7 +15651,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:34.186</t>
+          <t>2026/6/30 00:31:34.186</t>
         </is>
       </c>
       <c r="C381" t="n">
@@ -15691,7 +15691,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:39.441</t>
+          <t>2026/6/30 00:31:39.441</t>
         </is>
       </c>
       <c r="C382" t="n">
@@ -15731,7 +15731,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:44.100</t>
+          <t>2026/6/30 00:31:44.100</t>
         </is>
       </c>
       <c r="C383" t="n">
@@ -15771,7 +15771,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:48.791</t>
+          <t>2026/6/30 00:31:48.791</t>
         </is>
       </c>
       <c r="C384" t="n">
@@ -15811,7 +15811,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:54.060</t>
+          <t>2026/6/30 00:31:54.060</t>
         </is>
       </c>
       <c r="C385" t="n">
@@ -15851,7 +15851,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>2026/6/29 23:31:59.050</t>
+          <t>2026/6/30 00:31:59.050</t>
         </is>
       </c>
       <c r="C386" t="n">
@@ -15891,7 +15891,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:03.988</t>
+          <t>2026/6/30 00:32:03.988</t>
         </is>
       </c>
       <c r="C387" t="n">
@@ -15931,7 +15931,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:08.642</t>
+          <t>2026/6/30 00:32:08.642</t>
         </is>
       </c>
       <c r="C388" t="n">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:13.645</t>
+          <t>2026/6/30 00:32:13.645</t>
         </is>
       </c>
       <c r="C389" t="n">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:18.929</t>
+          <t>2026/6/30 00:32:18.929</t>
         </is>
       </c>
       <c r="C390" t="n">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:28.251</t>
+          <t>2026/6/30 00:32:28.251</t>
         </is>
       </c>
       <c r="C391" t="n">
@@ -16091,7 +16091,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:32.922</t>
+          <t>2026/6/30 00:32:32.922</t>
         </is>
       </c>
       <c r="C392" t="n">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:38.516</t>
+          <t>2026/6/30 00:32:38.516</t>
         </is>
       </c>
       <c r="C393" t="n">
@@ -16171,7 +16171,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:43.162</t>
+          <t>2026/6/30 00:32:43.162</t>
         </is>
       </c>
       <c r="C394" t="n">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:47.847</t>
+          <t>2026/6/30 00:32:47.847</t>
         </is>
       </c>
       <c r="C395" t="n">
@@ -16251,7 +16251,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:52.499</t>
+          <t>2026/6/30 00:32:52.499</t>
         </is>
       </c>
       <c r="C396" t="n">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>2026/6/29 23:32:57.807</t>
+          <t>2026/6/30 00:32:57.807</t>
         </is>
       </c>
       <c r="C397" t="n">
@@ -16331,7 +16331,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:02.459</t>
+          <t>2026/6/30 00:33:02.459</t>
         </is>
       </c>
       <c r="C398" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:07.123</t>
+          <t>2026/6/30 00:33:07.123</t>
         </is>
       </c>
       <c r="C399" t="n">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:11.781</t>
+          <t>2026/6/30 00:33:11.781</t>
         </is>
       </c>
       <c r="C400" t="n">
@@ -16451,7 +16451,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:17.389</t>
+          <t>2026/6/30 00:33:17.389</t>
         </is>
       </c>
       <c r="C401" t="n">
@@ -16491,7 +16491,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:22.033</t>
+          <t>2026/6/30 00:33:22.033</t>
         </is>
       </c>
       <c r="C402" t="n">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:26.663</t>
+          <t>2026/6/30 00:33:26.663</t>
         </is>
       </c>
       <c r="C403" t="n">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:31.325</t>
+          <t>2026/6/30 00:33:31.325</t>
         </is>
       </c>
       <c r="C404" t="n">
@@ -16611,7 +16611,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:36.655</t>
+          <t>2026/6/30 00:33:36.655</t>
         </is>
       </c>
       <c r="C405" t="n">
@@ -16651,7 +16651,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:41.611</t>
+          <t>2026/6/30 00:33:41.611</t>
         </is>
       </c>
       <c r="C406" t="n">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:46.258</t>
+          <t>2026/6/30 00:33:46.258</t>
         </is>
       </c>
       <c r="C407" t="n">
@@ -16731,7 +16731,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:50.929</t>
+          <t>2026/6/30 00:33:50.929</t>
         </is>
       </c>
       <c r="C408" t="n">
@@ -16771,7 +16771,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>2026/6/29 23:33:56.830</t>
+          <t>2026/6/30 00:33:56.830</t>
         </is>
       </c>
       <c r="C409" t="n">
@@ -16811,7 +16811,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:01.503</t>
+          <t>2026/6/30 00:34:01.503</t>
         </is>
       </c>
       <c r="C410" t="n">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:06.196</t>
+          <t>2026/6/30 00:34:06.196</t>
         </is>
       </c>
       <c r="C411" t="n">
@@ -16891,7 +16891,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:10.824</t>
+          <t>2026/6/30 00:34:10.824</t>
         </is>
       </c>
       <c r="C412" t="n">
@@ -16931,7 +16931,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:16.116</t>
+          <t>2026/6/30 00:34:16.116</t>
         </is>
       </c>
       <c r="C413" t="n">
@@ -16971,7 +16971,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:21.093</t>
+          <t>2026/6/30 00:34:21.093</t>
         </is>
       </c>
       <c r="C414" t="n">
@@ -17011,7 +17011,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:25.746</t>
+          <t>2026/6/30 00:34:25.746</t>
         </is>
       </c>
       <c r="C415" t="n">
@@ -17051,7 +17051,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:30.434</t>
+          <t>2026/6/30 00:34:30.434</t>
         </is>
       </c>
       <c r="C416" t="n">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:35.721</t>
+          <t>2026/6/30 00:34:35.721</t>
         </is>
       </c>
       <c r="C417" t="n">
@@ -17131,7 +17131,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:40.691</t>
+          <t>2026/6/30 00:34:40.691</t>
         </is>
       </c>
       <c r="C418" t="n">
@@ -17171,7 +17171,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:45.354</t>
+          <t>2026/6/30 00:34:45.354</t>
         </is>
       </c>
       <c r="C419" t="n">
@@ -17211,7 +17211,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:50.002</t>
+          <t>2026/6/30 00:34:50.002</t>
         </is>
       </c>
       <c r="C420" t="n">
@@ -17251,7 +17251,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>2026/6/29 23:34:55.576</t>
+          <t>2026/6/30 00:34:55.576</t>
         </is>
       </c>
       <c r="C421" t="n">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:00.588</t>
+          <t>2026/6/30 00:35:00.588</t>
         </is>
       </c>
       <c r="C422" t="n">
@@ -17331,7 +17331,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:05.212</t>
+          <t>2026/6/30 00:35:05.212</t>
         </is>
       </c>
       <c r="C423" t="n">
@@ -17371,7 +17371,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:09.895</t>
+          <t>2026/6/30 00:35:09.895</t>
         </is>
       </c>
       <c r="C424" t="n">
@@ -17411,7 +17411,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:14.893</t>
+          <t>2026/6/30 00:35:14.893</t>
         </is>
       </c>
       <c r="C425" t="n">
@@ -17451,7 +17451,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:20.177</t>
+          <t>2026/6/30 00:35:20.177</t>
         </is>
       </c>
       <c r="C426" t="n">
@@ -17491,7 +17491,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:24.826</t>
+          <t>2026/6/30 00:35:24.826</t>
         </is>
       </c>
       <c r="C427" t="n">
@@ -17531,7 +17531,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:29.492</t>
+          <t>2026/6/30 00:35:29.492</t>
         </is>
       </c>
       <c r="C428" t="n">
@@ -17571,7 +17571,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:34.439</t>
+          <t>2026/6/30 00:35:34.439</t>
         </is>
       </c>
       <c r="C429" t="n">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:39.452</t>
+          <t>2026/6/30 00:35:39.452</t>
         </is>
       </c>
       <c r="C430" t="n">
@@ -17651,7 +17651,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:44.098</t>
+          <t>2026/6/30 00:35:44.098</t>
         </is>
       </c>
       <c r="C431" t="n">
@@ -17691,7 +17691,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:48.726</t>
+          <t>2026/6/30 00:35:48.726</t>
         </is>
       </c>
       <c r="C432" t="n">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:53.754</t>
+          <t>2026/6/30 00:35:53.754</t>
         </is>
       </c>
       <c r="C433" t="n">
@@ -17771,7 +17771,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>2026/6/29 23:35:59.325</t>
+          <t>2026/6/30 00:35:59.325</t>
         </is>
       </c>
       <c r="C434" t="n">
@@ -17811,7 +17811,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:03.983</t>
+          <t>2026/6/30 00:36:03.983</t>
         </is>
       </c>
       <c r="C435" t="n">
@@ -17851,7 +17851,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:13.611</t>
+          <t>2026/6/30 00:36:13.611</t>
         </is>
       </c>
       <c r="C436" t="n">
@@ -17891,7 +17891,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:13.611</t>
+          <t>2026/6/30 00:36:13.611</t>
         </is>
       </c>
       <c r="C437" t="n">
@@ -17931,7 +17931,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:18.928</t>
+          <t>2026/6/30 00:36:18.928</t>
         </is>
       </c>
       <c r="C438" t="n">
@@ -17971,7 +17971,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:28.231</t>
+          <t>2026/6/30 00:36:28.231</t>
         </is>
       </c>
       <c r="C439" t="n">
@@ -18011,7 +18011,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:32.885</t>
+          <t>2026/6/30 00:36:32.885</t>
         </is>
       </c>
       <c r="C440" t="n">
@@ -18051,7 +18051,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:37.857</t>
+          <t>2026/6/30 00:36:37.857</t>
         </is>
       </c>
       <c r="C441" t="n">
@@ -18091,7 +18091,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:42.501</t>
+          <t>2026/6/30 00:36:42.501</t>
         </is>
       </c>
       <c r="C442" t="n">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:47.177</t>
+          <t>2026/6/30 00:36:47.177</t>
         </is>
       </c>
       <c r="C443" t="n">
@@ -18171,7 +18171,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:51.859</t>
+          <t>2026/6/30 00:36:51.859</t>
         </is>
       </c>
       <c r="C444" t="n">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>2026/6/29 23:36:57.781</t>
+          <t>2026/6/30 00:36:57.781</t>
         </is>
       </c>
       <c r="C445" t="n">
@@ -18251,7 +18251,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:02.396</t>
+          <t>2026/6/30 00:37:02.396</t>
         </is>
       </c>
       <c r="C446" t="n">
@@ -18291,7 +18291,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:07.099</t>
+          <t>2026/6/30 00:37:07.099</t>
         </is>
       </c>
       <c r="C447" t="n">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:11.741</t>
+          <t>2026/6/30 00:37:11.741</t>
         </is>
       </c>
       <c r="C448" t="n">
@@ -18371,7 +18371,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:17.354</t>
+          <t>2026/6/30 00:37:17.354</t>
         </is>
       </c>
       <c r="C449" t="n">
@@ -18411,7 +18411,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:22.005</t>
+          <t>2026/6/30 00:37:22.005</t>
         </is>
       </c>
       <c r="C450" t="n">
@@ -18451,7 +18451,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:26.694</t>
+          <t>2026/6/30 00:37:26.694</t>
         </is>
       </c>
       <c r="C451" t="n">
@@ -18491,7 +18491,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:31.345</t>
+          <t>2026/6/30 00:37:31.345</t>
         </is>
       </c>
       <c r="C452" t="n">
@@ -18531,7 +18531,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:36.629</t>
+          <t>2026/6/30 00:37:36.629</t>
         </is>
       </c>
       <c r="C453" t="n">
@@ -18571,7 +18571,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:41.571</t>
+          <t>2026/6/30 00:37:41.571</t>
         </is>
       </c>
       <c r="C454" t="n">
@@ -18611,7 +18611,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:46.243</t>
+          <t>2026/6/30 00:37:46.243</t>
         </is>
       </c>
       <c r="C455" t="n">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:50.907</t>
+          <t>2026/6/30 00:37:50.907</t>
         </is>
       </c>
       <c r="C456" t="n">
@@ -18691,7 +18691,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>2026/6/29 23:37:56.833</t>
+          <t>2026/6/30 00:37:56.833</t>
         </is>
       </c>
       <c r="C457" t="n">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:02.085</t>
+          <t>2026/6/30 00:38:02.085</t>
         </is>
       </c>
       <c r="C458" t="n">
@@ -18771,7 +18771,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:06.765</t>
+          <t>2026/6/30 00:38:06.765</t>
         </is>
       </c>
       <c r="C459" t="n">
@@ -18811,7 +18811,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:11.452</t>
+          <t>2026/6/30 00:38:11.452</t>
         </is>
       </c>
       <c r="C460" t="n">
@@ -18851,7 +18851,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:16.716</t>
+          <t>2026/6/30 00:38:16.716</t>
         </is>
       </c>
       <c r="C461" t="n">
@@ -18891,7 +18891,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:21.684</t>
+          <t>2026/6/30 00:38:21.684</t>
         </is>
       </c>
       <c r="C462" t="n">
@@ -18931,7 +18931,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:26.335</t>
+          <t>2026/6/30 00:38:26.335</t>
         </is>
       </c>
       <c r="C463" t="n">
@@ -18971,7 +18971,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:31.022</t>
+          <t>2026/6/30 00:38:31.022</t>
         </is>
       </c>
       <c r="C464" t="n">
@@ -19011,7 +19011,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:36.302</t>
+          <t>2026/6/30 00:38:36.302</t>
         </is>
       </c>
       <c r="C465" t="n">
@@ -19051,7 +19051,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:41.304</t>
+          <t>2026/6/30 00:38:41.304</t>
         </is>
       </c>
       <c r="C466" t="n">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:45.936</t>
+          <t>2026/6/30 00:38:45.936</t>
         </is>
       </c>
       <c r="C467" t="n">
@@ -19131,7 +19131,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:50.622</t>
+          <t>2026/6/30 00:38:50.622</t>
         </is>
       </c>
       <c r="C468" t="n">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>2026/6/29 23:38:56.505</t>
+          <t>2026/6/30 00:38:56.505</t>
         </is>
       </c>
       <c r="C469" t="n">
@@ -19211,7 +19211,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:01.178</t>
+          <t>2026/6/30 00:39:01.178</t>
         </is>
       </c>
       <c r="C470" t="n">
@@ -19251,7 +19251,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:05.853</t>
+          <t>2026/6/30 00:39:05.853</t>
         </is>
       </c>
       <c r="C471" t="n">
@@ -19291,7 +19291,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:10.506</t>
+          <t>2026/6/30 00:39:10.506</t>
         </is>
       </c>
       <c r="C472" t="n">
@@ -19331,7 +19331,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:15.794</t>
+          <t>2026/6/30 00:39:15.794</t>
         </is>
       </c>
       <c r="C473" t="n">
@@ -19371,7 +19371,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:20.787</t>
+          <t>2026/6/30 00:39:20.787</t>
         </is>
       </c>
       <c r="C474" t="n">
@@ -19411,7 +19411,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:25.420</t>
+          <t>2026/6/30 00:39:25.420</t>
         </is>
       </c>
       <c r="C475" t="n">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:30.095</t>
+          <t>2026/6/30 00:39:30.095</t>
         </is>
       </c>
       <c r="C476" t="n">
@@ -19491,7 +19491,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:35.404</t>
+          <t>2026/6/30 00:39:35.404</t>
         </is>
       </c>
       <c r="C477" t="n">
@@ -19531,7 +19531,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:40.322</t>
+          <t>2026/6/30 00:39:40.322</t>
         </is>
       </c>
       <c r="C478" t="n">
@@ -19571,7 +19571,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:45.037</t>
+          <t>2026/6/30 00:39:45.037</t>
         </is>
       </c>
       <c r="C479" t="n">
@@ -19611,7 +19611,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:49.679</t>
+          <t>2026/6/30 00:39:49.679</t>
         </is>
       </c>
       <c r="C480" t="n">
@@ -19651,7 +19651,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>2026/6/29 23:39:55.268</t>
+          <t>2026/6/30 00:39:55.268</t>
         </is>
       </c>
       <c r="C481" t="n">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:00.228</t>
+          <t>2026/6/30 00:40:00.228</t>
         </is>
       </c>
       <c r="C482" t="n">
@@ -19731,7 +19731,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:04.880</t>
+          <t>2026/6/30 00:40:04.880</t>
         </is>
       </c>
       <c r="C483" t="n">
@@ -19771,7 +19771,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:09.594</t>
+          <t>2026/6/30 00:40:09.594</t>
         </is>
       </c>
       <c r="C484" t="n">
@@ -19811,7 +19811,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:14.535</t>
+          <t>2026/6/30 00:40:14.535</t>
         </is>
       </c>
       <c r="C485" t="n">
@@ -19851,7 +19851,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:19.504</t>
+          <t>2026/6/30 00:40:19.504</t>
         </is>
       </c>
       <c r="C486" t="n">
@@ -19891,7 +19891,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:24.152</t>
+          <t>2026/6/30 00:40:24.152</t>
         </is>
       </c>
       <c r="C487" t="n">
@@ -19931,7 +19931,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:28.854</t>
+          <t>2026/6/30 00:40:28.854</t>
         </is>
       </c>
       <c r="C488" t="n">
@@ -19971,7 +19971,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:33.798</t>
+          <t>2026/6/30 00:40:33.798</t>
         </is>
       </c>
       <c r="C489" t="n">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:39.089</t>
+          <t>2026/6/30 00:40:39.089</t>
         </is>
       </c>
       <c r="C490" t="n">
@@ -20051,7 +20051,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:48.409</t>
+          <t>2026/6/30 00:40:48.409</t>
         </is>
       </c>
       <c r="C491" t="n">
@@ -20091,7 +20091,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:53.424</t>
+          <t>2026/6/30 00:40:53.424</t>
         </is>
       </c>
       <c r="C492" t="n">
@@ -20131,7 +20131,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:53.424</t>
+          <t>2026/6/30 00:40:53.424</t>
         </is>
       </c>
       <c r="C493" t="n">
@@ -20171,7 +20171,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>2026/6/29 23:40:59.033</t>
+          <t>2026/6/30 00:40:59.033</t>
         </is>
       </c>
       <c r="C494" t="n">
@@ -20211,7 +20211,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:08.307</t>
+          <t>2026/6/30 00:41:08.307</t>
         </is>
       </c>
       <c r="C495" t="n">
@@ -20251,7 +20251,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:12.991</t>
+          <t>2026/6/30 00:41:12.991</t>
         </is>
       </c>
       <c r="C496" t="n">
@@ -20291,7 +20291,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:17.624</t>
+          <t>2026/6/30 00:41:17.624</t>
         </is>
       </c>
       <c r="C497" t="n">
@@ -20331,7 +20331,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:22.313</t>
+          <t>2026/6/30 00:41:22.313</t>
         </is>
       </c>
       <c r="C498" t="n">
@@ -20371,7 +20371,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:26.954</t>
+          <t>2026/6/30 00:41:26.954</t>
         </is>
       </c>
       <c r="C499" t="n">
@@ -20411,7 +20411,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:31.610</t>
+          <t>2026/6/30 00:41:31.610</t>
         </is>
       </c>
       <c r="C500" t="n">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:36.289</t>
+          <t>2026/6/30 00:41:36.289</t>
         </is>
       </c>
       <c r="C501" t="n">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:40.953</t>
+          <t>2026/6/30 00:41:40.953</t>
         </is>
       </c>
       <c r="C502" t="n">
@@ -20531,7 +20531,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:45.604</t>
+          <t>2026/6/30 00:41:45.604</t>
         </is>
       </c>
       <c r="C503" t="n">
@@ -20571,7 +20571,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:50.260</t>
+          <t>2026/6/30 00:41:50.260</t>
         </is>
       </c>
       <c r="C504" t="n">
@@ -20611,7 +20611,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:54.944</t>
+          <t>2026/6/30 00:41:54.944</t>
         </is>
       </c>
       <c r="C505" t="n">
@@ -20651,7 +20651,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>2026/6/29 23:41:59.608</t>
+          <t>2026/6/30 00:41:59.608</t>
         </is>
       </c>
       <c r="C506" t="n">
@@ -20691,7 +20691,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:04.268</t>
+          <t>2026/6/30 00:42:04.268</t>
         </is>
       </c>
       <c r="C507" t="n">
@@ -20731,7 +20731,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:08.930</t>
+          <t>2026/6/30 00:42:08.930</t>
         </is>
       </c>
       <c r="C508" t="n">
@@ -20771,7 +20771,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:18.229</t>
+          <t>2026/6/30 00:42:18.229</t>
         </is>
       </c>
       <c r="C509" t="n">
@@ -20811,7 +20811,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:22.947</t>
+          <t>2026/6/30 00:42:22.947</t>
         </is>
       </c>
       <c r="C510" t="n">
@@ -20851,7 +20851,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:27.553</t>
+          <t>2026/6/30 00:42:27.553</t>
         </is>
       </c>
       <c r="C511" t="n">
@@ -20891,7 +20891,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:32.260</t>
+          <t>2026/6/30 00:42:32.260</t>
         </is>
       </c>
       <c r="C512" t="n">
@@ -20931,7 +20931,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:36.923</t>
+          <t>2026/6/30 00:42:36.923</t>
         </is>
       </c>
       <c r="C513" t="n">
@@ -20971,7 +20971,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:41.548</t>
+          <t>2026/6/30 00:42:41.548</t>
         </is>
       </c>
       <c r="C514" t="n">
@@ -21011,7 +21011,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:46.209</t>
+          <t>2026/6/30 00:42:46.209</t>
         </is>
       </c>
       <c r="C515" t="n">
@@ -21051,7 +21051,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:50.903</t>
+          <t>2026/6/30 00:42:50.903</t>
         </is>
       </c>
       <c r="C516" t="n">
@@ -21091,7 +21091,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>2026/6/29 23:42:55.536</t>
+          <t>2026/6/30 00:42:55.536</t>
         </is>
       </c>
       <c r="C517" t="n">
@@ -21131,7 +21131,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:00.218</t>
+          <t>2026/6/30 00:43:00.218</t>
         </is>
       </c>
       <c r="C518" t="n">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:04.864</t>
+          <t>2026/6/30 00:43:04.864</t>
         </is>
       </c>
       <c r="C519" t="n">
@@ -21211,7 +21211,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:09.545</t>
+          <t>2026/6/30 00:43:09.545</t>
         </is>
       </c>
       <c r="C520" t="n">
@@ -21251,7 +21251,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:14.213</t>
+          <t>2026/6/30 00:43:14.213</t>
         </is>
       </c>
       <c r="C521" t="n">
@@ -21291,7 +21291,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:18.902</t>
+          <t>2026/6/30 00:43:18.902</t>
         </is>
       </c>
       <c r="C522" t="n">
@@ -21331,7 +21331,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:28.197</t>
+          <t>2026/6/30 00:43:28.197</t>
         </is>
       </c>
       <c r="C523" t="n">
@@ -21371,7 +21371,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:32.863</t>
+          <t>2026/6/30 00:43:32.863</t>
         </is>
       </c>
       <c r="C524" t="n">
@@ -21411,7 +21411,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:37.515</t>
+          <t>2026/6/30 00:43:37.515</t>
         </is>
       </c>
       <c r="C525" t="n">
@@ -21451,7 +21451,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:42.192</t>
+          <t>2026/6/30 00:43:42.192</t>
         </is>
       </c>
       <c r="C526" t="n">
@@ -21491,7 +21491,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:46.809</t>
+          <t>2026/6/30 00:43:46.809</t>
         </is>
       </c>
       <c r="C527" t="n">
@@ -21531,7 +21531,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:51.479</t>
+          <t>2026/6/30 00:43:51.479</t>
         </is>
       </c>
       <c r="C528" t="n">
@@ -21571,7 +21571,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>2026/6/29 23:43:56.158</t>
+          <t>2026/6/30 00:43:56.158</t>
         </is>
       </c>
       <c r="C529" t="n">
@@ -21611,7 +21611,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:00.834</t>
+          <t>2026/6/30 00:44:00.834</t>
         </is>
       </c>
       <c r="C530" t="n">
@@ -21651,7 +21651,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:05.503</t>
+          <t>2026/6/30 00:44:05.503</t>
         </is>
       </c>
       <c r="C531" t="n">
@@ -21691,7 +21691,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:10.163</t>
+          <t>2026/6/30 00:44:10.163</t>
         </is>
       </c>
       <c r="C532" t="n">
@@ -21731,7 +21731,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:14.839</t>
+          <t>2026/6/30 00:44:14.839</t>
         </is>
       </c>
       <c r="C533" t="n">
@@ -21771,7 +21771,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:19.489</t>
+          <t>2026/6/30 00:44:19.489</t>
         </is>
       </c>
       <c r="C534" t="n">
@@ -21811,7 +21811,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:24.164</t>
+          <t>2026/6/30 00:44:24.164</t>
         </is>
       </c>
       <c r="C535" t="n">
@@ -21851,7 +21851,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:33.461</t>
+          <t>2026/6/30 00:44:33.461</t>
         </is>
       </c>
       <c r="C536" t="n">
@@ -21891,7 +21891,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:38.138</t>
+          <t>2026/6/30 00:44:38.138</t>
         </is>
       </c>
       <c r="C537" t="n">
@@ -21931,7 +21931,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:42.766</t>
+          <t>2026/6/30 00:44:42.766</t>
         </is>
       </c>
       <c r="C538" t="n">
@@ -21971,7 +21971,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:47.469</t>
+          <t>2026/6/30 00:44:47.469</t>
         </is>
       </c>
       <c r="C539" t="n">
@@ -22011,7 +22011,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:52.125</t>
+          <t>2026/6/30 00:44:52.125</t>
         </is>
       </c>
       <c r="C540" t="n">
@@ -22051,7 +22051,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>2026/6/29 23:44:56.776</t>
+          <t>2026/6/30 00:44:56.776</t>
         </is>
       </c>
       <c r="C541" t="n">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="B542" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:01.439</t>
+          <t>2026/6/30 00:45:01.439</t>
         </is>
       </c>
       <c r="C542" t="n">
@@ -22131,7 +22131,7 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:06.096</t>
+          <t>2026/6/30 00:45:06.096</t>
         </is>
       </c>
       <c r="C543" t="n">
@@ -22171,7 +22171,7 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:10.742</t>
+          <t>2026/6/30 00:45:10.742</t>
         </is>
       </c>
       <c r="C544" t="n">
@@ -22211,7 +22211,7 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:15.418</t>
+          <t>2026/6/30 00:45:15.418</t>
         </is>
       </c>
       <c r="C545" t="n">
@@ -22251,7 +22251,7 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:20.094</t>
+          <t>2026/6/30 00:45:20.094</t>
         </is>
       </c>
       <c r="C546" t="n">
@@ -22291,7 +22291,7 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:24.743</t>
+          <t>2026/6/30 00:45:24.743</t>
         </is>
       </c>
       <c r="C547" t="n">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:29.412</t>
+          <t>2026/6/30 00:45:29.412</t>
         </is>
       </c>
       <c r="C548" t="n">
@@ -22371,7 +22371,7 @@
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:34.079</t>
+          <t>2026/6/30 00:45:34.079</t>
         </is>
       </c>
       <c r="C549" t="n">
@@ -22411,7 +22411,7 @@
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:43.399</t>
+          <t>2026/6/30 00:45:43.399</t>
         </is>
       </c>
       <c r="C550" t="n">
@@ -22451,7 +22451,7 @@
       </c>
       <c r="B551" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:48.067</t>
+          <t>2026/6/30 00:45:48.067</t>
         </is>
       </c>
       <c r="C551" t="n">
@@ -22491,7 +22491,7 @@
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:52.747</t>
+          <t>2026/6/30 00:45:52.747</t>
         </is>
       </c>
       <c r="C552" t="n">
@@ -22531,7 +22531,7 @@
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>2026/6/29 23:45:57.395</t>
+          <t>2026/6/30 00:45:57.395</t>
         </is>
       </c>
       <c r="C553" t="n">
@@ -22571,7 +22571,7 @@
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:02.048</t>
+          <t>2026/6/30 00:46:02.048</t>
         </is>
       </c>
       <c r="C554" t="n">
@@ -22611,7 +22611,7 @@
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:06.704</t>
+          <t>2026/6/30 00:46:06.704</t>
         </is>
       </c>
       <c r="C555" t="n">
@@ -22651,7 +22651,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:11.392</t>
+          <t>2026/6/30 00:46:11.392</t>
         </is>
       </c>
       <c r="C556" t="n">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:16.029</t>
+          <t>2026/6/30 00:46:16.029</t>
         </is>
       </c>
       <c r="C557" t="n">
@@ -22731,7 +22731,7 @@
       </c>
       <c r="B558" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:20.717</t>
+          <t>2026/6/30 00:46:20.717</t>
         </is>
       </c>
       <c r="C558" t="n">
@@ -22771,7 +22771,7 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:25.349</t>
+          <t>2026/6/30 00:46:25.349</t>
         </is>
       </c>
       <c r="C559" t="n">
@@ -22811,7 +22811,7 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:30.059</t>
+          <t>2026/6/30 00:46:30.059</t>
         </is>
       </c>
       <c r="C560" t="n">
@@ -22851,7 +22851,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:34.702</t>
+          <t>2026/6/30 00:46:34.702</t>
         </is>
       </c>
       <c r="C561" t="n">
@@ -22891,7 +22891,7 @@
       </c>
       <c r="B562" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:39.355</t>
+          <t>2026/6/30 00:46:39.355</t>
         </is>
       </c>
       <c r="C562" t="n">
@@ -22931,7 +22931,7 @@
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:44.043</t>
+          <t>2026/6/30 00:46:44.043</t>
         </is>
       </c>
       <c r="C563" t="n">
@@ -22971,7 +22971,7 @@
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:53.368</t>
+          <t>2026/6/30 00:46:53.368</t>
         </is>
       </c>
       <c r="C564" t="n">
@@ -23011,7 +23011,7 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>2026/6/29 23:46:58.012</t>
+          <t>2026/6/30 00:46:58.012</t>
         </is>
       </c>
       <c r="C565" t="n">
@@ -23051,7 +23051,7 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:02.643</t>
+          <t>2026/6/30 00:47:02.643</t>
         </is>
       </c>
       <c r="C566" t="n">
@@ -23091,7 +23091,7 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:07.336</t>
+          <t>2026/6/30 00:47:07.336</t>
         </is>
       </c>
       <c r="C567" t="n">
@@ -23131,7 +23131,7 @@
       </c>
       <c r="B568" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:11.974</t>
+          <t>2026/6/30 00:47:11.974</t>
         </is>
       </c>
       <c r="C568" t="n">
@@ -23171,7 +23171,7 @@
       </c>
       <c r="B569" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:16.667</t>
+          <t>2026/6/30 00:47:16.667</t>
         </is>
       </c>
       <c r="C569" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="B570" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:21.315</t>
+          <t>2026/6/30 00:47:21.315</t>
         </is>
       </c>
       <c r="C570" t="n">
@@ -23251,7 +23251,7 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:25.996</t>
+          <t>2026/6/30 00:47:25.996</t>
         </is>
       </c>
       <c r="C571" t="n">
@@ -23291,7 +23291,7 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:30.647</t>
+          <t>2026/6/30 00:47:30.647</t>
         </is>
       </c>
       <c r="C572" t="n">
@@ -23331,7 +23331,7 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:35.298</t>
+          <t>2026/6/30 00:47:35.298</t>
         </is>
       </c>
       <c r="C573" t="n">
@@ -23371,7 +23371,7 @@
       </c>
       <c r="B574" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:39.964</t>
+          <t>2026/6/30 00:47:39.964</t>
         </is>
       </c>
       <c r="C574" t="n">
@@ -23411,7 +23411,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:44.604</t>
+          <t>2026/6/30 00:47:44.604</t>
         </is>
       </c>
       <c r="C575" t="n">
@@ -23451,7 +23451,7 @@
       </c>
       <c r="B576" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:49.274</t>
+          <t>2026/6/30 00:47:49.274</t>
         </is>
       </c>
       <c r="C576" t="n">
@@ -23491,7 +23491,7 @@
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>2026/6/29 23:47:53.949</t>
+          <t>2026/6/30 00:47:53.949</t>
         </is>
       </c>
       <c r="C577" t="n">
